--- a/regulation-to-excel/assets/regulation-template.xlsx
+++ b/regulation-to-excel/assets/regulation-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0aadf8b376f94f87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfa42f3c9a4514488"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,19 +19,10 @@
     <x:t xml:space="preserve">监管要求</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">是否适用于腾讯云</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">客户责任解读</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">内部实践情况</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">出处</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">客户可以使用的服务</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">备注</x:t>
@@ -204,7 +195,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -283,13 +274,25 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="0"/>
     <x:cellStyle name="常规 4" xfId="1"/>
   </x:cellStyles>
-  <x:dxfs count="2">
+  <x:dxfs count="6">
     <x:dxf>
       <x:fill>
         <x:patternFill>
@@ -301,6 +304,34 @@
       <x:fill>
         <x:patternFill>
           <x:bgColor theme="0" tint="-0.24995"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FF00B050"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFBFBFBF"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FF00B050"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFBFBFBF"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -533,36 +564,36 @@
       <x:c r="E1" s="22"/>
       <x:c r="F1" s="22"/>
       <x:c r="G1" s="22"/>
-      <x:c r="H1" s="23" t="s">
+      <x:c r="H1" s="23" t="str">
+        <x:v>是否适用于目标环境</x:v>
+      </x:c>
+      <x:c r="I1" s="25" t="str">
+        <x:v>相关主体责任解读</x:v>
+      </x:c>
+      <x:c r="J1" s="20" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I1" s="25" t="s">
+      <x:c r="K1" s="18" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J1" s="20" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="K1" s="18" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="L1" s="20" t="s">
-        <x:v>7</x:v>
+      <x:c r="L1" s="20" t="str">
+        <x:v>可使用的产品与服务</x:v>
       </x:c>
       <x:c r="M1" s="18" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="N1" s="20" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="45.95000076293945" customHeight="1">
       <x:c r="A2" s="21"/>
       <x:c r="B2" s="22"/>
       <x:c r="C2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E2" s="1" t="str">
         <x:v>原始语言版条款（原文）</x:v>
@@ -588,14 +619,14 @@
       <x:c r="D3" s="5"/>
       <x:c r="E3" s="6"/>
       <x:c r="F3" s="6"/>
-      <x:c r="G3" s="7"/>
+      <x:c r="G3" s="6"/>
       <x:c r="H3" s="8"/>
       <x:c r="I3" s="6"/>
       <x:c r="J3" s="6"/>
       <x:c r="K3" s="6"/>
-      <x:c r="L3" s="5"/>
-      <x:c r="M3" s="5"/>
-      <x:c r="N3" s="5"/>
+      <x:c r="L3" s="6"/>
+      <x:c r="M3" s="6"/>
+      <x:c r="N3" s="6"/>
     </x:row>
     <x:row r="4" ht="409.5" customHeight="1">
       <x:c r="A4" s="5"/>
@@ -604,14 +635,14 @@
       <x:c r="D4" s="5"/>
       <x:c r="E4" s="6"/>
       <x:c r="F4" s="6"/>
-      <x:c r="G4" s="7"/>
+      <x:c r="G4" s="6"/>
       <x:c r="H4" s="8"/>
       <x:c r="I4" s="6"/>
       <x:c r="J4" s="6"/>
       <x:c r="K4" s="6"/>
-      <x:c r="L4" s="5"/>
-      <x:c r="M4" s="5"/>
-      <x:c r="N4" s="5"/>
+      <x:c r="L4" s="6"/>
+      <x:c r="M4" s="6"/>
+      <x:c r="N4" s="6"/>
     </x:row>
     <x:row r="5" ht="409.5" customHeight="1">
       <x:c r="A5" s="5"/>
@@ -620,14 +651,14 @@
       <x:c r="D5" s="5"/>
       <x:c r="E5" s="6"/>
       <x:c r="F5" s="6"/>
-      <x:c r="G5" s="7"/>
+      <x:c r="G5" s="6"/>
       <x:c r="H5" s="8"/>
       <x:c r="I5" s="6"/>
       <x:c r="J5" s="6"/>
       <x:c r="K5" s="6"/>
-      <x:c r="L5" s="5"/>
-      <x:c r="M5" s="9"/>
-      <x:c r="N5" s="5"/>
+      <x:c r="L5" s="6"/>
+      <x:c r="M5" s="6"/>
+      <x:c r="N5" s="6"/>
     </x:row>
     <x:row r="6" ht="409.5" customHeight="1">
       <x:c r="A6" s="5"/>
@@ -636,14 +667,14 @@
       <x:c r="D6" s="5"/>
       <x:c r="E6" s="6"/>
       <x:c r="F6" s="6"/>
-      <x:c r="G6" s="7"/>
+      <x:c r="G6" s="6"/>
       <x:c r="H6" s="8"/>
       <x:c r="I6" s="6"/>
       <x:c r="J6" s="6"/>
       <x:c r="K6" s="6"/>
-      <x:c r="L6" s="5"/>
-      <x:c r="M6" s="9"/>
-      <x:c r="N6" s="5"/>
+      <x:c r="L6" s="6"/>
+      <x:c r="M6" s="6"/>
+      <x:c r="N6" s="6"/>
     </x:row>
     <x:row r="7" ht="409.5" customHeight="1">
       <x:c r="A7" s="5"/>
@@ -651,15 +682,15 @@
       <x:c r="C7" s="5"/>
       <x:c r="D7" s="5"/>
       <x:c r="E7" s="6"/>
-      <x:c r="F7" s="10"/>
-      <x:c r="G7" s="7"/>
+      <x:c r="F7" s="6"/>
+      <x:c r="G7" s="6"/>
       <x:c r="H7" s="8"/>
       <x:c r="I7" s="6"/>
       <x:c r="J7" s="6"/>
       <x:c r="K7" s="6"/>
-      <x:c r="L7" s="5"/>
-      <x:c r="M7" s="9"/>
-      <x:c r="N7" s="5"/>
+      <x:c r="L7" s="6"/>
+      <x:c r="M7" s="6"/>
+      <x:c r="N7" s="6"/>
     </x:row>
     <x:row r="8" ht="173" customHeight="1">
       <x:c r="A8" s="5"/>
@@ -667,15 +698,15 @@
       <x:c r="C8" s="5"/>
       <x:c r="D8" s="5"/>
       <x:c r="E8" s="6"/>
-      <x:c r="F8" s="10"/>
+      <x:c r="F8" s="6"/>
       <x:c r="G8" s="6"/>
       <x:c r="H8" s="8"/>
       <x:c r="I8" s="6"/>
       <x:c r="J8" s="6"/>
       <x:c r="K8" s="6"/>
       <x:c r="L8" s="6"/>
-      <x:c r="M8" s="11"/>
-      <x:c r="N8" s="5"/>
+      <x:c r="M8" s="6"/>
+      <x:c r="N8" s="6"/>
     </x:row>
     <x:row r="9" ht="409.5" customHeight="1">
       <x:c r="A9" s="5"/>
@@ -683,15 +714,15 @@
       <x:c r="C9" s="5"/>
       <x:c r="D9" s="5"/>
       <x:c r="E9" s="6"/>
-      <x:c r="F9" s="10"/>
+      <x:c r="F9" s="6"/>
       <x:c r="G9" s="6"/>
       <x:c r="H9" s="8"/>
-      <x:c r="I9" s="12"/>
+      <x:c r="I9" s="6"/>
       <x:c r="J9" s="6"/>
       <x:c r="K9" s="6"/>
       <x:c r="L9" s="6"/>
-      <x:c r="M9" s="11"/>
-      <x:c r="N9" s="7"/>
+      <x:c r="M9" s="6"/>
+      <x:c r="N9" s="6"/>
     </x:row>
     <x:row r="10" ht="156.5" customHeight="1">
       <x:c r="A10" s="5"/>
@@ -699,15 +730,15 @@
       <x:c r="C10" s="5"/>
       <x:c r="D10" s="5"/>
       <x:c r="E10" s="6"/>
-      <x:c r="F10" s="10"/>
-      <x:c r="G10" s="10"/>
+      <x:c r="F10" s="6"/>
+      <x:c r="G10" s="6"/>
       <x:c r="H10" s="8"/>
       <x:c r="I10" s="6"/>
-      <x:c r="J10" s="13"/>
+      <x:c r="J10" s="6"/>
       <x:c r="K10" s="6"/>
       <x:c r="L10" s="6"/>
-      <x:c r="M10" s="11"/>
-      <x:c r="N10" s="7"/>
+      <x:c r="M10" s="6"/>
+      <x:c r="N10" s="6"/>
     </x:row>
     <x:row r="11" ht="409.5" customHeight="1">
       <x:c r="A11" s="5"/>
@@ -715,15 +746,15 @@
       <x:c r="C11" s="5"/>
       <x:c r="D11" s="5"/>
       <x:c r="E11" s="6"/>
-      <x:c r="F11" s="10"/>
+      <x:c r="F11" s="6"/>
       <x:c r="G11" s="6"/>
       <x:c r="H11" s="8"/>
       <x:c r="I11" s="6"/>
       <x:c r="J11" s="6"/>
-      <x:c r="K11" s="12"/>
+      <x:c r="K11" s="6"/>
       <x:c r="L11" s="6"/>
-      <x:c r="M11" s="11"/>
-      <x:c r="N11" s="14"/>
+      <x:c r="M11" s="6"/>
+      <x:c r="N11" s="6"/>
     </x:row>
     <x:row r="12" ht="156.5" customHeight="1">
       <x:c r="A12" s="5"/>
@@ -731,7 +762,7 @@
       <x:c r="C12" s="5"/>
       <x:c r="D12" s="5"/>
       <x:c r="E12" s="6"/>
-      <x:c r="F12" s="10"/>
+      <x:c r="F12" s="6"/>
       <x:c r="G12" s="6"/>
       <x:c r="H12" s="8"/>
       <x:c r="I12" s="6"/>
@@ -739,7 +770,7 @@
       <x:c r="K12" s="6"/>
       <x:c r="L12" s="6"/>
       <x:c r="M12" s="6"/>
-      <x:c r="N12" s="15"/>
+      <x:c r="N12" s="6"/>
     </x:row>
     <x:row r="13" ht="409.5" customHeight="1">
       <x:c r="A13" s="5"/>
@@ -747,7 +778,7 @@
       <x:c r="C13" s="5"/>
       <x:c r="D13" s="5"/>
       <x:c r="E13" s="6"/>
-      <x:c r="F13" s="10"/>
+      <x:c r="F13" s="6"/>
       <x:c r="G13" s="6"/>
       <x:c r="H13" s="8"/>
       <x:c r="I13" s="6"/>
@@ -755,7 +786,7 @@
       <x:c r="K13" s="6"/>
       <x:c r="L13" s="6"/>
       <x:c r="M13" s="6"/>
-      <x:c r="N13" s="7"/>
+      <x:c r="N13" s="6"/>
     </x:row>
     <x:row r="14" ht="409.5" customHeight="1">
       <x:c r="A14" s="5"/>
@@ -769,9 +800,9 @@
       <x:c r="I14" s="6"/>
       <x:c r="J14" s="6"/>
       <x:c r="K14" s="6"/>
-      <x:c r="L14" s="7"/>
-      <x:c r="M14" s="7"/>
-      <x:c r="N14" s="16"/>
+      <x:c r="L14" s="6"/>
+      <x:c r="M14" s="6"/>
+      <x:c r="N14" s="6"/>
     </x:row>
     <x:row r="15" ht="409.5" customHeight="1">
       <x:c r="A15" s="5"/>
@@ -785,9 +816,9 @@
       <x:c r="I15" s="6"/>
       <x:c r="J15" s="6"/>
       <x:c r="K15" s="6"/>
-      <x:c r="L15" s="7"/>
+      <x:c r="L15" s="6"/>
       <x:c r="M15" s="6"/>
-      <x:c r="N15" s="7"/>
+      <x:c r="N15" s="6"/>
     </x:row>
     <x:row r="16" ht="288.5" customHeight="1">
       <x:c r="A16" s="5"/>
@@ -801,9 +832,9 @@
       <x:c r="I16" s="6"/>
       <x:c r="J16" s="6"/>
       <x:c r="K16" s="6"/>
-      <x:c r="L16" s="7"/>
+      <x:c r="L16" s="6"/>
       <x:c r="M16" s="6"/>
-      <x:c r="N16" s="7"/>
+      <x:c r="N16" s="6"/>
     </x:row>
     <x:row r="17" ht="409.5" customHeight="1">
       <x:c r="A17" s="5"/>
@@ -817,9 +848,9 @@
       <x:c r="I17" s="6"/>
       <x:c r="J17" s="6"/>
       <x:c r="K17" s="6"/>
-      <x:c r="L17" s="7"/>
-      <x:c r="M17" s="7"/>
-      <x:c r="N17" s="7"/>
+      <x:c r="L17" s="6"/>
+      <x:c r="M17" s="6"/>
+      <x:c r="N17" s="6"/>
     </x:row>
     <x:row r="18" ht="305" customHeight="1">
       <x:c r="A18" s="5"/>
@@ -833,9 +864,9 @@
       <x:c r="I18" s="6"/>
       <x:c r="J18" s="6"/>
       <x:c r="K18" s="6"/>
-      <x:c r="L18" s="7"/>
+      <x:c r="L18" s="6"/>
       <x:c r="M18" s="6"/>
-      <x:c r="N18" s="7"/>
+      <x:c r="N18" s="6"/>
     </x:row>
     <x:row r="19" ht="409.5" customHeight="1">
       <x:c r="A19" s="5"/>
@@ -849,9 +880,9 @@
       <x:c r="I19" s="6"/>
       <x:c r="J19" s="6"/>
       <x:c r="K19" s="6"/>
-      <x:c r="L19" s="7"/>
+      <x:c r="L19" s="6"/>
       <x:c r="M19" s="6"/>
-      <x:c r="N19" s="7"/>
+      <x:c r="N19" s="6"/>
     </x:row>
     <x:row r="20" ht="409.5" customHeight="1">
       <x:c r="A20" s="5"/>
@@ -865,25 +896,25 @@
       <x:c r="I20" s="6"/>
       <x:c r="J20" s="6"/>
       <x:c r="K20" s="6"/>
-      <x:c r="L20" s="7"/>
-      <x:c r="M20" s="7"/>
-      <x:c r="N20" s="7"/>
+      <x:c r="L20" s="6"/>
+      <x:c r="M20" s="6"/>
+      <x:c r="N20" s="6"/>
     </x:row>
     <x:row r="21" ht="288.5" customHeight="1">
       <x:c r="A21" s="5"/>
       <x:c r="B21" s="5"/>
       <x:c r="C21" s="5"/>
       <x:c r="D21" s="5"/>
-      <x:c r="E21" s="7"/>
-      <x:c r="F21" s="10"/>
+      <x:c r="E21" s="6"/>
+      <x:c r="F21" s="6"/>
       <x:c r="G21" s="6"/>
       <x:c r="H21" s="8"/>
       <x:c r="I21" s="6"/>
       <x:c r="J21" s="6"/>
       <x:c r="K21" s="6"/>
-      <x:c r="L21" s="7"/>
+      <x:c r="L21" s="6"/>
       <x:c r="M21" s="6"/>
-      <x:c r="N21" s="7"/>
+      <x:c r="N21" s="6"/>
     </x:row>
     <x:row r="22" ht="409.5" customHeight="1">
       <x:c r="A22" s="5"/>
@@ -897,9 +928,9 @@
       <x:c r="I22" s="6"/>
       <x:c r="J22" s="6"/>
       <x:c r="K22" s="6"/>
-      <x:c r="L22" s="7"/>
+      <x:c r="L22" s="6"/>
       <x:c r="M22" s="6"/>
-      <x:c r="N22" s="7"/>
+      <x:c r="N22" s="6"/>
     </x:row>
     <x:row r="23" ht="409.5" customHeight="1">
       <x:c r="A23" s="5"/>
@@ -913,121 +944,121 @@
       <x:c r="I23" s="6"/>
       <x:c r="J23" s="6"/>
       <x:c r="K23" s="6"/>
-      <x:c r="L23" s="7"/>
-      <x:c r="M23" s="7"/>
-      <x:c r="N23" s="7"/>
+      <x:c r="L23" s="6"/>
+      <x:c r="M23" s="6"/>
+      <x:c r="N23" s="6"/>
     </x:row>
     <x:row r="24" ht="409.5" customHeight="1">
       <x:c r="A24" s="5"/>
       <x:c r="B24" s="5"/>
       <x:c r="C24" s="5"/>
       <x:c r="D24" s="5"/>
-      <x:c r="E24" s="7"/>
+      <x:c r="E24" s="6"/>
       <x:c r="F24" s="6"/>
       <x:c r="G24" s="6"/>
       <x:c r="H24" s="8"/>
       <x:c r="I24" s="6"/>
       <x:c r="J24" s="6"/>
       <x:c r="K24" s="6"/>
-      <x:c r="L24" s="7"/>
+      <x:c r="L24" s="6"/>
       <x:c r="M24" s="6"/>
-      <x:c r="N24" s="7"/>
+      <x:c r="N24" s="6"/>
     </x:row>
     <x:row r="25" ht="409.5" customHeight="1">
       <x:c r="A25" s="5"/>
       <x:c r="B25" s="5"/>
       <x:c r="C25" s="5"/>
       <x:c r="D25" s="5"/>
-      <x:c r="E25" s="7"/>
+      <x:c r="E25" s="6"/>
       <x:c r="F25" s="6"/>
       <x:c r="G25" s="6"/>
       <x:c r="H25" s="8"/>
       <x:c r="I25" s="6"/>
       <x:c r="J25" s="6"/>
       <x:c r="K25" s="6"/>
-      <x:c r="L25" s="7"/>
+      <x:c r="L25" s="6"/>
       <x:c r="M25" s="6"/>
-      <x:c r="N25" s="7"/>
+      <x:c r="N25" s="6"/>
     </x:row>
     <x:row r="26" ht="321.5" customHeight="1">
       <x:c r="A26" s="5"/>
       <x:c r="B26" s="5"/>
       <x:c r="C26" s="5"/>
       <x:c r="D26" s="5"/>
-      <x:c r="E26" s="7"/>
+      <x:c r="E26" s="6"/>
       <x:c r="F26" s="6"/>
       <x:c r="G26" s="6"/>
       <x:c r="H26" s="8"/>
       <x:c r="I26" s="6"/>
       <x:c r="J26" s="6"/>
       <x:c r="K26" s="6"/>
-      <x:c r="L26" s="7"/>
-      <x:c r="M26" s="7"/>
-      <x:c r="N26" s="7"/>
+      <x:c r="L26" s="6"/>
+      <x:c r="M26" s="6"/>
+      <x:c r="N26" s="6"/>
     </x:row>
     <x:row r="27" ht="409.5" customHeight="1">
       <x:c r="A27" s="5"/>
       <x:c r="B27" s="5"/>
       <x:c r="C27" s="5"/>
       <x:c r="D27" s="5"/>
-      <x:c r="E27" s="7"/>
+      <x:c r="E27" s="6"/>
       <x:c r="F27" s="6"/>
       <x:c r="G27" s="6"/>
       <x:c r="H27" s="8"/>
       <x:c r="I27" s="6"/>
       <x:c r="J27" s="6"/>
       <x:c r="K27" s="6"/>
-      <x:c r="L27" s="7"/>
+      <x:c r="L27" s="6"/>
       <x:c r="M27" s="6"/>
-      <x:c r="N27" s="7"/>
+      <x:c r="N27" s="6"/>
     </x:row>
     <x:row r="28" ht="409.5" customHeight="1">
       <x:c r="A28" s="5"/>
       <x:c r="B28" s="5"/>
       <x:c r="C28" s="5"/>
       <x:c r="D28" s="5"/>
-      <x:c r="E28" s="7"/>
+      <x:c r="E28" s="6"/>
       <x:c r="F28" s="6"/>
       <x:c r="G28" s="6"/>
       <x:c r="H28" s="8"/>
       <x:c r="I28" s="6"/>
       <x:c r="J28" s="6"/>
       <x:c r="K28" s="6"/>
-      <x:c r="L28" s="7"/>
+      <x:c r="L28" s="6"/>
       <x:c r="M28" s="6"/>
-      <x:c r="N28" s="7"/>
+      <x:c r="N28" s="6"/>
     </x:row>
     <x:row r="29" ht="107" customHeight="1">
       <x:c r="A29" s="5"/>
       <x:c r="B29" s="5"/>
       <x:c r="C29" s="5"/>
       <x:c r="D29" s="5"/>
-      <x:c r="E29" s="7"/>
+      <x:c r="E29" s="6"/>
       <x:c r="F29" s="6"/>
       <x:c r="G29" s="6"/>
       <x:c r="H29" s="8"/>
       <x:c r="I29" s="6"/>
       <x:c r="J29" s="6"/>
       <x:c r="K29" s="6"/>
-      <x:c r="L29" s="7"/>
+      <x:c r="L29" s="6"/>
       <x:c r="M29" s="6"/>
-      <x:c r="N29" s="7"/>
+      <x:c r="N29" s="6"/>
     </x:row>
     <x:row r="30" ht="409.5" customHeight="1">
       <x:c r="A30" s="5"/>
       <x:c r="B30" s="5"/>
       <x:c r="C30" s="5"/>
       <x:c r="D30" s="5"/>
-      <x:c r="E30" s="7"/>
+      <x:c r="E30" s="6"/>
       <x:c r="F30" s="6"/>
       <x:c r="G30" s="6"/>
       <x:c r="H30" s="8"/>
       <x:c r="I30" s="6"/>
       <x:c r="J30" s="6"/>
       <x:c r="K30" s="6"/>
-      <x:c r="L30" s="7"/>
+      <x:c r="L30" s="6"/>
       <x:c r="M30" s="6"/>
-      <x:c r="N30" s="7"/>
+      <x:c r="N30" s="6"/>
     </x:row>
     <x:row r="31" ht="107" customHeight="1">
       <x:c r="A31" s="5"/>
@@ -1037,285 +1068,285 @@
       <x:c r="E31" s="6"/>
       <x:c r="F31" s="6"/>
       <x:c r="G31" s="6"/>
-      <x:c r="H31" s="17"/>
+      <x:c r="H31" s="8"/>
       <x:c r="I31" s="6"/>
       <x:c r="J31" s="6"/>
       <x:c r="K31" s="6"/>
-      <x:c r="L31" s="7"/>
+      <x:c r="L31" s="6"/>
       <x:c r="M31" s="6"/>
-      <x:c r="N31" s="7"/>
+      <x:c r="N31" s="6"/>
     </x:row>
     <x:row r="32" ht="107" customHeight="1">
       <x:c r="A32" s="5"/>
       <x:c r="B32" s="5"/>
       <x:c r="C32" s="5"/>
       <x:c r="D32" s="5"/>
-      <x:c r="E32" s="7"/>
+      <x:c r="E32" s="6"/>
       <x:c r="F32" s="6"/>
       <x:c r="G32" s="6"/>
-      <x:c r="H32" s="17"/>
+      <x:c r="H32" s="8"/>
       <x:c r="I32" s="6"/>
       <x:c r="J32" s="6"/>
       <x:c r="K32" s="6"/>
-      <x:c r="L32" s="7"/>
+      <x:c r="L32" s="6"/>
       <x:c r="M32" s="6"/>
-      <x:c r="N32" s="7"/>
+      <x:c r="N32" s="6"/>
     </x:row>
     <x:row r="33" ht="15" customHeight="1">
-      <x:c r="A33"/>
-      <x:c r="B33"/>
-      <x:c r="C33"/>
-      <x:c r="D33"/>
-      <x:c r="E33"/>
-      <x:c r="F33"/>
-      <x:c r="G33"/>
-      <x:c r="H33"/>
-      <x:c r="I33"/>
-      <x:c r="J33"/>
-      <x:c r="K33"/>
-      <x:c r="L33"/>
-      <x:c r="M33"/>
-      <x:c r="N33"/>
+      <x:c r="A33" s="5"/>
+      <x:c r="B33" s="5"/>
+      <x:c r="C33" s="5"/>
+      <x:c r="D33" s="5"/>
+      <x:c r="E33" s="6"/>
+      <x:c r="F33" s="6"/>
+      <x:c r="G33" s="6"/>
+      <x:c r="H33" s="8"/>
+      <x:c r="I33" s="6"/>
+      <x:c r="J33" s="6"/>
+      <x:c r="K33" s="6"/>
+      <x:c r="L33" s="6"/>
+      <x:c r="M33" s="6"/>
+      <x:c r="N33" s="6"/>
     </x:row>
     <x:row r="34" ht="15" customHeight="1">
-      <x:c r="A34"/>
-      <x:c r="B34"/>
-      <x:c r="C34"/>
-      <x:c r="D34"/>
-      <x:c r="E34"/>
-      <x:c r="F34"/>
-      <x:c r="G34"/>
-      <x:c r="H34"/>
-      <x:c r="I34"/>
-      <x:c r="J34"/>
-      <x:c r="K34"/>
-      <x:c r="L34"/>
-      <x:c r="M34"/>
-      <x:c r="N34"/>
+      <x:c r="A34" s="5"/>
+      <x:c r="B34" s="5"/>
+      <x:c r="C34" s="5"/>
+      <x:c r="D34" s="5"/>
+      <x:c r="E34" s="6"/>
+      <x:c r="F34" s="6"/>
+      <x:c r="G34" s="6"/>
+      <x:c r="H34" s="8"/>
+      <x:c r="I34" s="6"/>
+      <x:c r="J34" s="6"/>
+      <x:c r="K34" s="6"/>
+      <x:c r="L34" s="6"/>
+      <x:c r="M34" s="6"/>
+      <x:c r="N34" s="6"/>
     </x:row>
     <x:row r="35" ht="15" customHeight="1">
-      <x:c r="A35"/>
-      <x:c r="B35"/>
-      <x:c r="C35"/>
-      <x:c r="D35"/>
-      <x:c r="E35"/>
-      <x:c r="F35"/>
-      <x:c r="G35"/>
-      <x:c r="H35"/>
-      <x:c r="I35"/>
-      <x:c r="J35"/>
-      <x:c r="K35"/>
-      <x:c r="L35"/>
-      <x:c r="M35"/>
-      <x:c r="N35"/>
+      <x:c r="A35" s="5"/>
+      <x:c r="B35" s="5"/>
+      <x:c r="C35" s="5"/>
+      <x:c r="D35" s="5"/>
+      <x:c r="E35" s="6"/>
+      <x:c r="F35" s="6"/>
+      <x:c r="G35" s="6"/>
+      <x:c r="H35" s="8"/>
+      <x:c r="I35" s="6"/>
+      <x:c r="J35" s="6"/>
+      <x:c r="K35" s="6"/>
+      <x:c r="L35" s="6"/>
+      <x:c r="M35" s="6"/>
+      <x:c r="N35" s="6"/>
     </x:row>
     <x:row r="36" ht="15" customHeight="1">
-      <x:c r="A36"/>
-      <x:c r="B36"/>
-      <x:c r="C36"/>
-      <x:c r="D36"/>
-      <x:c r="E36"/>
-      <x:c r="F36"/>
-      <x:c r="G36"/>
-      <x:c r="H36"/>
-      <x:c r="I36"/>
-      <x:c r="J36"/>
-      <x:c r="K36"/>
-      <x:c r="L36"/>
-      <x:c r="M36"/>
-      <x:c r="N36"/>
+      <x:c r="A36" s="5"/>
+      <x:c r="B36" s="5"/>
+      <x:c r="C36" s="5"/>
+      <x:c r="D36" s="5"/>
+      <x:c r="E36" s="6"/>
+      <x:c r="F36" s="6"/>
+      <x:c r="G36" s="6"/>
+      <x:c r="H36" s="8"/>
+      <x:c r="I36" s="6"/>
+      <x:c r="J36" s="6"/>
+      <x:c r="K36" s="6"/>
+      <x:c r="L36" s="6"/>
+      <x:c r="M36" s="6"/>
+      <x:c r="N36" s="6"/>
     </x:row>
     <x:row r="37" ht="15" customHeight="1">
-      <x:c r="A37"/>
-      <x:c r="B37"/>
-      <x:c r="C37"/>
-      <x:c r="D37"/>
-      <x:c r="E37"/>
-      <x:c r="F37"/>
-      <x:c r="G37"/>
-      <x:c r="H37"/>
-      <x:c r="I37"/>
-      <x:c r="J37"/>
-      <x:c r="K37"/>
-      <x:c r="L37"/>
-      <x:c r="M37"/>
-      <x:c r="N37"/>
+      <x:c r="A37" s="5"/>
+      <x:c r="B37" s="5"/>
+      <x:c r="C37" s="5"/>
+      <x:c r="D37" s="5"/>
+      <x:c r="E37" s="6"/>
+      <x:c r="F37" s="6"/>
+      <x:c r="G37" s="6"/>
+      <x:c r="H37" s="8"/>
+      <x:c r="I37" s="6"/>
+      <x:c r="J37" s="6"/>
+      <x:c r="K37" s="6"/>
+      <x:c r="L37" s="6"/>
+      <x:c r="M37" s="6"/>
+      <x:c r="N37" s="6"/>
     </x:row>
     <x:row r="38" ht="15" customHeight="1">
-      <x:c r="A38"/>
-      <x:c r="B38"/>
-      <x:c r="C38"/>
-      <x:c r="D38"/>
-      <x:c r="E38"/>
-      <x:c r="F38"/>
-      <x:c r="G38"/>
-      <x:c r="H38"/>
-      <x:c r="I38"/>
-      <x:c r="J38"/>
-      <x:c r="K38"/>
-      <x:c r="L38"/>
-      <x:c r="M38"/>
-      <x:c r="N38"/>
+      <x:c r="A38" s="5"/>
+      <x:c r="B38" s="5"/>
+      <x:c r="C38" s="5"/>
+      <x:c r="D38" s="5"/>
+      <x:c r="E38" s="6"/>
+      <x:c r="F38" s="6"/>
+      <x:c r="G38" s="6"/>
+      <x:c r="H38" s="8"/>
+      <x:c r="I38" s="6"/>
+      <x:c r="J38" s="6"/>
+      <x:c r="K38" s="6"/>
+      <x:c r="L38" s="6"/>
+      <x:c r="M38" s="6"/>
+      <x:c r="N38" s="6"/>
     </x:row>
     <x:row r="39" ht="15" customHeight="1">
-      <x:c r="A39"/>
-      <x:c r="B39"/>
-      <x:c r="C39"/>
-      <x:c r="D39"/>
-      <x:c r="E39"/>
-      <x:c r="F39"/>
-      <x:c r="G39"/>
-      <x:c r="H39"/>
-      <x:c r="I39"/>
-      <x:c r="J39"/>
-      <x:c r="K39"/>
-      <x:c r="L39"/>
-      <x:c r="M39"/>
-      <x:c r="N39"/>
+      <x:c r="A39" s="5"/>
+      <x:c r="B39" s="5"/>
+      <x:c r="C39" s="5"/>
+      <x:c r="D39" s="5"/>
+      <x:c r="E39" s="6"/>
+      <x:c r="F39" s="6"/>
+      <x:c r="G39" s="6"/>
+      <x:c r="H39" s="8"/>
+      <x:c r="I39" s="6"/>
+      <x:c r="J39" s="6"/>
+      <x:c r="K39" s="6"/>
+      <x:c r="L39" s="6"/>
+      <x:c r="M39" s="6"/>
+      <x:c r="N39" s="6"/>
     </x:row>
     <x:row r="40" ht="15" customHeight="1">
-      <x:c r="A40"/>
-      <x:c r="B40"/>
-      <x:c r="C40"/>
-      <x:c r="D40"/>
-      <x:c r="E40"/>
-      <x:c r="F40"/>
-      <x:c r="G40"/>
-      <x:c r="H40"/>
-      <x:c r="I40"/>
-      <x:c r="J40"/>
-      <x:c r="K40"/>
-      <x:c r="L40"/>
-      <x:c r="M40"/>
-      <x:c r="N40"/>
+      <x:c r="A40" s="5"/>
+      <x:c r="B40" s="5"/>
+      <x:c r="C40" s="5"/>
+      <x:c r="D40" s="5"/>
+      <x:c r="E40" s="6"/>
+      <x:c r="F40" s="6"/>
+      <x:c r="G40" s="6"/>
+      <x:c r="H40" s="8"/>
+      <x:c r="I40" s="6"/>
+      <x:c r="J40" s="6"/>
+      <x:c r="K40" s="6"/>
+      <x:c r="L40" s="6"/>
+      <x:c r="M40" s="6"/>
+      <x:c r="N40" s="6"/>
     </x:row>
     <x:row r="41" ht="15" customHeight="1">
-      <x:c r="A41"/>
-      <x:c r="B41"/>
-      <x:c r="C41"/>
-      <x:c r="D41"/>
-      <x:c r="E41"/>
-      <x:c r="F41"/>
-      <x:c r="G41"/>
-      <x:c r="H41"/>
-      <x:c r="I41"/>
-      <x:c r="J41"/>
-      <x:c r="K41"/>
-      <x:c r="L41"/>
-      <x:c r="M41"/>
-      <x:c r="N41"/>
+      <x:c r="A41" s="5"/>
+      <x:c r="B41" s="5"/>
+      <x:c r="C41" s="5"/>
+      <x:c r="D41" s="5"/>
+      <x:c r="E41" s="6"/>
+      <x:c r="F41" s="6"/>
+      <x:c r="G41" s="6"/>
+      <x:c r="H41" s="8"/>
+      <x:c r="I41" s="6"/>
+      <x:c r="J41" s="6"/>
+      <x:c r="K41" s="6"/>
+      <x:c r="L41" s="6"/>
+      <x:c r="M41" s="6"/>
+      <x:c r="N41" s="6"/>
     </x:row>
     <x:row r="42" ht="15" customHeight="1">
-      <x:c r="A42"/>
-      <x:c r="B42"/>
-      <x:c r="C42"/>
-      <x:c r="D42"/>
-      <x:c r="E42"/>
-      <x:c r="F42"/>
-      <x:c r="G42"/>
-      <x:c r="H42"/>
-      <x:c r="I42"/>
-      <x:c r="J42"/>
-      <x:c r="K42"/>
-      <x:c r="L42"/>
-      <x:c r="M42"/>
-      <x:c r="N42"/>
+      <x:c r="A42" s="5"/>
+      <x:c r="B42" s="5"/>
+      <x:c r="C42" s="5"/>
+      <x:c r="D42" s="5"/>
+      <x:c r="E42" s="6"/>
+      <x:c r="F42" s="6"/>
+      <x:c r="G42" s="6"/>
+      <x:c r="H42" s="8"/>
+      <x:c r="I42" s="6"/>
+      <x:c r="J42" s="6"/>
+      <x:c r="K42" s="6"/>
+      <x:c r="L42" s="6"/>
+      <x:c r="M42" s="6"/>
+      <x:c r="N42" s="6"/>
     </x:row>
     <x:row r="43" ht="15" customHeight="1">
-      <x:c r="A43"/>
-      <x:c r="B43"/>
-      <x:c r="C43"/>
-      <x:c r="D43"/>
-      <x:c r="E43"/>
-      <x:c r="F43"/>
-      <x:c r="G43"/>
-      <x:c r="H43"/>
-      <x:c r="I43"/>
-      <x:c r="J43"/>
-      <x:c r="K43"/>
-      <x:c r="L43"/>
-      <x:c r="M43"/>
-      <x:c r="N43"/>
+      <x:c r="A43" s="5"/>
+      <x:c r="B43" s="5"/>
+      <x:c r="C43" s="5"/>
+      <x:c r="D43" s="5"/>
+      <x:c r="E43" s="6"/>
+      <x:c r="F43" s="6"/>
+      <x:c r="G43" s="6"/>
+      <x:c r="H43" s="8"/>
+      <x:c r="I43" s="6"/>
+      <x:c r="J43" s="6"/>
+      <x:c r="K43" s="6"/>
+      <x:c r="L43" s="6"/>
+      <x:c r="M43" s="6"/>
+      <x:c r="N43" s="6"/>
     </x:row>
     <x:row r="44" ht="15" customHeight="1">
-      <x:c r="A44"/>
-      <x:c r="B44"/>
-      <x:c r="C44"/>
-      <x:c r="D44"/>
-      <x:c r="E44"/>
-      <x:c r="F44"/>
-      <x:c r="G44"/>
-      <x:c r="H44"/>
-      <x:c r="I44"/>
-      <x:c r="J44"/>
-      <x:c r="K44"/>
-      <x:c r="L44"/>
-      <x:c r="M44"/>
-      <x:c r="N44"/>
+      <x:c r="A44" s="5"/>
+      <x:c r="B44" s="5"/>
+      <x:c r="C44" s="5"/>
+      <x:c r="D44" s="5"/>
+      <x:c r="E44" s="6"/>
+      <x:c r="F44" s="6"/>
+      <x:c r="G44" s="6"/>
+      <x:c r="H44" s="8"/>
+      <x:c r="I44" s="6"/>
+      <x:c r="J44" s="6"/>
+      <x:c r="K44" s="6"/>
+      <x:c r="L44" s="6"/>
+      <x:c r="M44" s="6"/>
+      <x:c r="N44" s="6"/>
     </x:row>
     <x:row r="45" ht="15" customHeight="1">
-      <x:c r="A45"/>
-      <x:c r="B45"/>
-      <x:c r="C45"/>
-      <x:c r="D45"/>
-      <x:c r="E45"/>
-      <x:c r="F45"/>
-      <x:c r="G45"/>
-      <x:c r="H45"/>
-      <x:c r="I45"/>
-      <x:c r="J45"/>
-      <x:c r="K45"/>
-      <x:c r="L45"/>
-      <x:c r="M45"/>
-      <x:c r="N45"/>
+      <x:c r="A45" s="5"/>
+      <x:c r="B45" s="5"/>
+      <x:c r="C45" s="5"/>
+      <x:c r="D45" s="5"/>
+      <x:c r="E45" s="6"/>
+      <x:c r="F45" s="6"/>
+      <x:c r="G45" s="6"/>
+      <x:c r="H45" s="8"/>
+      <x:c r="I45" s="6"/>
+      <x:c r="J45" s="6"/>
+      <x:c r="K45" s="6"/>
+      <x:c r="L45" s="6"/>
+      <x:c r="M45" s="6"/>
+      <x:c r="N45" s="6"/>
     </x:row>
     <x:row r="46" ht="15" customHeight="1">
-      <x:c r="A46"/>
-      <x:c r="B46"/>
-      <x:c r="C46"/>
-      <x:c r="D46"/>
-      <x:c r="E46"/>
-      <x:c r="F46"/>
-      <x:c r="G46"/>
-      <x:c r="H46"/>
-      <x:c r="I46"/>
-      <x:c r="J46"/>
-      <x:c r="K46"/>
-      <x:c r="L46"/>
-      <x:c r="M46"/>
-      <x:c r="N46"/>
+      <x:c r="A46" s="5"/>
+      <x:c r="B46" s="5"/>
+      <x:c r="C46" s="5"/>
+      <x:c r="D46" s="5"/>
+      <x:c r="E46" s="6"/>
+      <x:c r="F46" s="6"/>
+      <x:c r="G46" s="6"/>
+      <x:c r="H46" s="8"/>
+      <x:c r="I46" s="6"/>
+      <x:c r="J46" s="6"/>
+      <x:c r="K46" s="6"/>
+      <x:c r="L46" s="6"/>
+      <x:c r="M46" s="6"/>
+      <x:c r="N46" s="6"/>
     </x:row>
     <x:row r="47" ht="15" customHeight="1">
-      <x:c r="A47"/>
-      <x:c r="B47"/>
-      <x:c r="C47"/>
-      <x:c r="D47"/>
-      <x:c r="E47"/>
-      <x:c r="F47"/>
-      <x:c r="G47"/>
-      <x:c r="H47"/>
-      <x:c r="I47"/>
-      <x:c r="J47"/>
-      <x:c r="K47"/>
-      <x:c r="L47"/>
-      <x:c r="M47"/>
-      <x:c r="N47"/>
+      <x:c r="A47" s="5"/>
+      <x:c r="B47" s="5"/>
+      <x:c r="C47" s="5"/>
+      <x:c r="D47" s="5"/>
+      <x:c r="E47" s="6"/>
+      <x:c r="F47" s="6"/>
+      <x:c r="G47" s="6"/>
+      <x:c r="H47" s="8"/>
+      <x:c r="I47" s="6"/>
+      <x:c r="J47" s="6"/>
+      <x:c r="K47" s="6"/>
+      <x:c r="L47" s="6"/>
+      <x:c r="M47" s="6"/>
+      <x:c r="N47" s="6"/>
     </x:row>
     <x:row r="48" ht="15" customHeight="1">
-      <x:c r="A48"/>
-      <x:c r="B48"/>
-      <x:c r="C48"/>
-      <x:c r="D48"/>
-      <x:c r="E48"/>
-      <x:c r="F48"/>
-      <x:c r="G48"/>
-      <x:c r="H48"/>
-      <x:c r="I48"/>
-      <x:c r="J48"/>
-      <x:c r="K48"/>
-      <x:c r="L48"/>
-      <x:c r="M48"/>
-      <x:c r="N48"/>
+      <x:c r="A48" s="5"/>
+      <x:c r="B48" s="5"/>
+      <x:c r="C48" s="5"/>
+      <x:c r="D48" s="5"/>
+      <x:c r="E48" s="6"/>
+      <x:c r="F48" s="6"/>
+      <x:c r="G48" s="6"/>
+      <x:c r="H48" s="8"/>
+      <x:c r="I48" s="6"/>
+      <x:c r="J48" s="6"/>
+      <x:c r="K48" s="6"/>
+      <x:c r="L48" s="6"/>
+      <x:c r="M48" s="6"/>
+      <x:c r="N48" s="6"/>
     </x:row>
     <x:row r="49" ht="15" customHeight="1"/>
     <x:row r="50" ht="15" customHeight="1"/>
@@ -1381,7 +1412,7 @@
     <x:mergeCell ref="I1:I2"/>
     <x:mergeCell ref="J1:J2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="H3:H99">
+  <x:conditionalFormatting sqref="H49:H99">
     <x:cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <x:formula>"否"</x:formula>
     </x:cfRule>
@@ -1389,8 +1420,19 @@
       <x:formula>"是"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H99">
+  <x:conditionalFormatting sqref="H3:H48">
+    <x:cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+      <x:formula>"是"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+      <x:formula>"否"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H49:H99">
+      <x:formula1>"是,否"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H48">
       <x:formula1>"是,否"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
